--- a/DEV/org.openl.rules.test/test-resources/functionality/Range-DoubleNumber.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/Range-DoubleNumber.xlsx
@@ -119,604 +119,604 @@
     </r>
   </si>
   <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>2K</t>
-  </si>
-  <si>
-    <t>3K</t>
-  </si>
-  <si>
-    <t>4K</t>
-  </si>
-  <si>
-    <t>5K</t>
-  </si>
-  <si>
-    <t>6K</t>
-  </si>
-  <si>
-    <t>7K</t>
-  </si>
-  <si>
-    <t>8K</t>
-  </si>
-  <si>
-    <t>9K</t>
-  </si>
-  <si>
-    <t>10K</t>
-  </si>
-  <si>
-    <t>11K</t>
-  </si>
-  <si>
-    <t>12K</t>
-  </si>
-  <si>
-    <t>13K</t>
-  </si>
-  <si>
-    <t>14K</t>
-  </si>
-  <si>
-    <t>15K</t>
-  </si>
-  <si>
-    <t>16K</t>
-  </si>
-  <si>
-    <t>17K</t>
-  </si>
-  <si>
-    <t>18K</t>
-  </si>
-  <si>
-    <t>19K</t>
-  </si>
-  <si>
-    <t>20K</t>
-  </si>
-  <si>
-    <t>21K</t>
-  </si>
-  <si>
-    <t>22K</t>
-  </si>
-  <si>
-    <t>23K</t>
-  </si>
-  <si>
-    <t>24K</t>
-  </si>
-  <si>
-    <t>25K</t>
-  </si>
-  <si>
-    <t>26K</t>
-  </si>
-  <si>
-    <t>27K</t>
-  </si>
-  <si>
-    <t>28K</t>
-  </si>
-  <si>
-    <t>29K</t>
-  </si>
-  <si>
-    <t>30K</t>
-  </si>
-  <si>
-    <t>31K</t>
-  </si>
-  <si>
-    <t>32K</t>
-  </si>
-  <si>
-    <t>33K</t>
-  </si>
-  <si>
-    <t>34K</t>
-  </si>
-  <si>
-    <t>35K</t>
-  </si>
-  <si>
-    <t>36K</t>
-  </si>
-  <si>
-    <t>37K</t>
-  </si>
-  <si>
-    <t>38K</t>
-  </si>
-  <si>
-    <t>39K</t>
-  </si>
-  <si>
-    <t>40K</t>
-  </si>
-  <si>
-    <t>41K</t>
-  </si>
-  <si>
-    <t>42K</t>
-  </si>
-  <si>
-    <t>43K</t>
-  </si>
-  <si>
-    <t>44K</t>
-  </si>
-  <si>
-    <t>45K</t>
-  </si>
-  <si>
-    <t>46K</t>
-  </si>
-  <si>
-    <t>47K</t>
-  </si>
-  <si>
-    <t>48K</t>
-  </si>
-  <si>
-    <t>49K</t>
-  </si>
-  <si>
-    <t>50K</t>
-  </si>
-  <si>
-    <t>51K</t>
-  </si>
-  <si>
-    <t>52K</t>
-  </si>
-  <si>
-    <t>53K</t>
-  </si>
-  <si>
-    <t>54K</t>
-  </si>
-  <si>
-    <t>55K</t>
-  </si>
-  <si>
-    <t>56K</t>
-  </si>
-  <si>
-    <t>57K</t>
-  </si>
-  <si>
-    <t>58K</t>
-  </si>
-  <si>
-    <t>59K</t>
-  </si>
-  <si>
-    <t>60K</t>
-  </si>
-  <si>
-    <t>61K</t>
-  </si>
-  <si>
-    <t>62K</t>
-  </si>
-  <si>
-    <t>63K</t>
-  </si>
-  <si>
-    <t>64K</t>
-  </si>
-  <si>
-    <t>65K</t>
-  </si>
-  <si>
-    <t>66K</t>
-  </si>
-  <si>
-    <t>67K</t>
-  </si>
-  <si>
-    <t>68K</t>
-  </si>
-  <si>
-    <t>69K</t>
-  </si>
-  <si>
-    <t>70K</t>
-  </si>
-  <si>
-    <t>71K</t>
-  </si>
-  <si>
-    <t>72K</t>
-  </si>
-  <si>
-    <t>73K</t>
-  </si>
-  <si>
-    <t>74K</t>
-  </si>
-  <si>
-    <t>75K</t>
-  </si>
-  <si>
-    <t>76K</t>
-  </si>
-  <si>
-    <t>77K</t>
-  </si>
-  <si>
-    <t>78K</t>
-  </si>
-  <si>
-    <t>79K</t>
-  </si>
-  <si>
-    <t>80K</t>
-  </si>
-  <si>
-    <t>81K</t>
-  </si>
-  <si>
-    <t>82K</t>
-  </si>
-  <si>
-    <t>83K</t>
-  </si>
-  <si>
-    <t>84K</t>
-  </si>
-  <si>
-    <t>85K</t>
-  </si>
-  <si>
-    <t>86K</t>
-  </si>
-  <si>
-    <t>87K</t>
-  </si>
-  <si>
-    <t>88K</t>
-  </si>
-  <si>
-    <t>89K</t>
-  </si>
-  <si>
-    <t>90K</t>
-  </si>
-  <si>
-    <t>91K</t>
-  </si>
-  <si>
-    <t>92K</t>
-  </si>
-  <si>
-    <t>93K</t>
-  </si>
-  <si>
-    <t>94K</t>
-  </si>
-  <si>
-    <t>95K</t>
-  </si>
-  <si>
-    <t>96K</t>
-  </si>
-  <si>
-    <t>97K</t>
-  </si>
-  <si>
-    <t>98K</t>
-  </si>
-  <si>
-    <t>99K</t>
-  </si>
-  <si>
-    <t>100K</t>
-  </si>
-  <si>
-    <t>101K</t>
-  </si>
-  <si>
-    <t>102K</t>
-  </si>
-  <si>
-    <t>103K</t>
-  </si>
-  <si>
-    <t>104K</t>
-  </si>
-  <si>
-    <t>105K</t>
-  </si>
-  <si>
-    <t>106K</t>
-  </si>
-  <si>
-    <t>107K</t>
-  </si>
-  <si>
-    <t>108K</t>
-  </si>
-  <si>
-    <t>109K</t>
-  </si>
-  <si>
-    <t>110K</t>
-  </si>
-  <si>
-    <t>111K</t>
-  </si>
-  <si>
-    <t>112K</t>
-  </si>
-  <si>
-    <t>113K</t>
-  </si>
-  <si>
-    <t>114K</t>
-  </si>
-  <si>
-    <t>115K</t>
-  </si>
-  <si>
-    <t>116K</t>
-  </si>
-  <si>
-    <t>117K</t>
-  </si>
-  <si>
-    <t>118K</t>
-  </si>
-  <si>
-    <t>119K</t>
-  </si>
-  <si>
-    <t>120K</t>
-  </si>
-  <si>
-    <t>121K</t>
-  </si>
-  <si>
-    <t>122K</t>
-  </si>
-  <si>
-    <t>123K</t>
-  </si>
-  <si>
-    <t>124K</t>
-  </si>
-  <si>
-    <t>125K</t>
-  </si>
-  <si>
-    <t>126K</t>
-  </si>
-  <si>
-    <t>127K</t>
-  </si>
-  <si>
-    <t>128K</t>
-  </si>
-  <si>
-    <t>129K</t>
-  </si>
-  <si>
-    <t>130K</t>
-  </si>
-  <si>
-    <t>131K</t>
-  </si>
-  <si>
-    <t>132K</t>
-  </si>
-  <si>
-    <t>133K</t>
-  </si>
-  <si>
-    <t>134K</t>
-  </si>
-  <si>
-    <t>135K</t>
-  </si>
-  <si>
-    <t>136K</t>
-  </si>
-  <si>
-    <t>137K</t>
-  </si>
-  <si>
-    <t>138K</t>
-  </si>
-  <si>
-    <t>139K</t>
-  </si>
-  <si>
-    <t>140K</t>
-  </si>
-  <si>
-    <t>141K</t>
-  </si>
-  <si>
-    <t>142K</t>
-  </si>
-  <si>
-    <t>143K</t>
-  </si>
-  <si>
-    <t>144K</t>
-  </si>
-  <si>
-    <t>145K</t>
-  </si>
-  <si>
-    <t>146K</t>
-  </si>
-  <si>
-    <t>147K</t>
-  </si>
-  <si>
-    <t>148K</t>
-  </si>
-  <si>
-    <t>149K</t>
-  </si>
-  <si>
-    <t>150K</t>
-  </si>
-  <si>
-    <t>151K</t>
-  </si>
-  <si>
-    <t>152K</t>
-  </si>
-  <si>
-    <t>153K</t>
-  </si>
-  <si>
-    <t>154K</t>
-  </si>
-  <si>
-    <t>155K</t>
-  </si>
-  <si>
-    <t>156K</t>
-  </si>
-  <si>
-    <t>157K</t>
-  </si>
-  <si>
-    <t>158K</t>
-  </si>
-  <si>
-    <t>159K</t>
-  </si>
-  <si>
-    <t>160K</t>
-  </si>
-  <si>
-    <t>161K</t>
-  </si>
-  <si>
-    <t>162K</t>
-  </si>
-  <si>
-    <t>163K</t>
-  </si>
-  <si>
-    <t>164K</t>
-  </si>
-  <si>
-    <t>165K</t>
-  </si>
-  <si>
-    <t>166K</t>
-  </si>
-  <si>
-    <t>167K</t>
-  </si>
-  <si>
-    <t>168K</t>
-  </si>
-  <si>
-    <t>169K</t>
-  </si>
-  <si>
-    <t>170K</t>
-  </si>
-  <si>
-    <t>171K</t>
-  </si>
-  <si>
-    <t>172K</t>
-  </si>
-  <si>
-    <t>173K</t>
-  </si>
-  <si>
-    <t>174K</t>
-  </si>
-  <si>
-    <t>175K</t>
-  </si>
-  <si>
-    <t>176K</t>
-  </si>
-  <si>
-    <t>177K</t>
-  </si>
-  <si>
-    <t>178K</t>
-  </si>
-  <si>
-    <t>179K</t>
-  </si>
-  <si>
-    <t>180K</t>
-  </si>
-  <si>
-    <t>181K</t>
-  </si>
-  <si>
-    <t>182K</t>
-  </si>
-  <si>
-    <t>183K</t>
-  </si>
-  <si>
-    <t>184K</t>
-  </si>
-  <si>
-    <t>185K</t>
-  </si>
-  <si>
-    <t>186K</t>
-  </si>
-  <si>
-    <t>187K</t>
-  </si>
-  <si>
-    <t>188K</t>
-  </si>
-  <si>
-    <t>189K</t>
-  </si>
-  <si>
-    <t>190K</t>
-  </si>
-  <si>
-    <t>191K</t>
-  </si>
-  <si>
-    <t>192K</t>
-  </si>
-  <si>
-    <t>193K</t>
-  </si>
-  <si>
-    <t>194K</t>
-  </si>
-  <si>
-    <t>195K</t>
-  </si>
-  <si>
-    <t>196K</t>
-  </si>
-  <si>
-    <t>197K</t>
-  </si>
-  <si>
-    <t>198K</t>
-  </si>
-  <si>
-    <t>199K</t>
-  </si>
-  <si>
-    <t>200K</t>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>4000</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>6000</t>
+  </si>
+  <si>
+    <t>7000</t>
+  </si>
+  <si>
+    <t>8000</t>
+  </si>
+  <si>
+    <t>9000</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>11000</t>
+  </si>
+  <si>
+    <t>12000</t>
+  </si>
+  <si>
+    <t>13000</t>
+  </si>
+  <si>
+    <t>14000</t>
+  </si>
+  <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>16000</t>
+  </si>
+  <si>
+    <t>17000</t>
+  </si>
+  <si>
+    <t>18000</t>
+  </si>
+  <si>
+    <t>19000</t>
+  </si>
+  <si>
+    <t>20000</t>
+  </si>
+  <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>22000</t>
+  </si>
+  <si>
+    <t>23000</t>
+  </si>
+  <si>
+    <t>24000</t>
+  </si>
+  <si>
+    <t>25000</t>
+  </si>
+  <si>
+    <t>26000</t>
+  </si>
+  <si>
+    <t>27000</t>
+  </si>
+  <si>
+    <t>28000</t>
+  </si>
+  <si>
+    <t>29000</t>
+  </si>
+  <si>
+    <t>30000</t>
+  </si>
+  <si>
+    <t>31000</t>
+  </si>
+  <si>
+    <t>32000</t>
+  </si>
+  <si>
+    <t>33000</t>
+  </si>
+  <si>
+    <t>34000</t>
+  </si>
+  <si>
+    <t>35000</t>
+  </si>
+  <si>
+    <t>36000</t>
+  </si>
+  <si>
+    <t>37000</t>
+  </si>
+  <si>
+    <t>38000</t>
+  </si>
+  <si>
+    <t>39000</t>
+  </si>
+  <si>
+    <t>40000</t>
+  </si>
+  <si>
+    <t>41000</t>
+  </si>
+  <si>
+    <t>42000</t>
+  </si>
+  <si>
+    <t>43000</t>
+  </si>
+  <si>
+    <t>44000</t>
+  </si>
+  <si>
+    <t>45000</t>
+  </si>
+  <si>
+    <t>46000</t>
+  </si>
+  <si>
+    <t>47000</t>
+  </si>
+  <si>
+    <t>48000</t>
+  </si>
+  <si>
+    <t>49000</t>
+  </si>
+  <si>
+    <t>50000</t>
+  </si>
+  <si>
+    <t>51000</t>
+  </si>
+  <si>
+    <t>52000</t>
+  </si>
+  <si>
+    <t>53000</t>
+  </si>
+  <si>
+    <t>54000</t>
+  </si>
+  <si>
+    <t>55000</t>
+  </si>
+  <si>
+    <t>56000</t>
+  </si>
+  <si>
+    <t>57000</t>
+  </si>
+  <si>
+    <t>58000</t>
+  </si>
+  <si>
+    <t>59000</t>
+  </si>
+  <si>
+    <t>60000</t>
+  </si>
+  <si>
+    <t>61000</t>
+  </si>
+  <si>
+    <t>62000</t>
+  </si>
+  <si>
+    <t>63000</t>
+  </si>
+  <si>
+    <t>64000</t>
+  </si>
+  <si>
+    <t>65000</t>
+  </si>
+  <si>
+    <t>66000</t>
+  </si>
+  <si>
+    <t>67000</t>
+  </si>
+  <si>
+    <t>68000</t>
+  </si>
+  <si>
+    <t>69000</t>
+  </si>
+  <si>
+    <t>70000</t>
+  </si>
+  <si>
+    <t>71000</t>
+  </si>
+  <si>
+    <t>72000</t>
+  </si>
+  <si>
+    <t>73000</t>
+  </si>
+  <si>
+    <t>74000</t>
+  </si>
+  <si>
+    <t>75000</t>
+  </si>
+  <si>
+    <t>76000</t>
+  </si>
+  <si>
+    <t>77000</t>
+  </si>
+  <si>
+    <t>78000</t>
+  </si>
+  <si>
+    <t>79000</t>
+  </si>
+  <si>
+    <t>80000</t>
+  </si>
+  <si>
+    <t>81000</t>
+  </si>
+  <si>
+    <t>82000</t>
+  </si>
+  <si>
+    <t>83000</t>
+  </si>
+  <si>
+    <t>84000</t>
+  </si>
+  <si>
+    <t>85000</t>
+  </si>
+  <si>
+    <t>86000</t>
+  </si>
+  <si>
+    <t>87000</t>
+  </si>
+  <si>
+    <t>88000</t>
+  </si>
+  <si>
+    <t>89000</t>
+  </si>
+  <si>
+    <t>90000</t>
+  </si>
+  <si>
+    <t>91000</t>
+  </si>
+  <si>
+    <t>92000</t>
+  </si>
+  <si>
+    <t>93000</t>
+  </si>
+  <si>
+    <t>94000</t>
+  </si>
+  <si>
+    <t>95000</t>
+  </si>
+  <si>
+    <t>96000</t>
+  </si>
+  <si>
+    <t>97000</t>
+  </si>
+  <si>
+    <t>98000</t>
+  </si>
+  <si>
+    <t>99000</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>101000</t>
+  </si>
+  <si>
+    <t>102000</t>
+  </si>
+  <si>
+    <t>103000</t>
+  </si>
+  <si>
+    <t>104000</t>
+  </si>
+  <si>
+    <t>105000</t>
+  </si>
+  <si>
+    <t>106000</t>
+  </si>
+  <si>
+    <t>107000</t>
+  </si>
+  <si>
+    <t>108000</t>
+  </si>
+  <si>
+    <t>109000</t>
+  </si>
+  <si>
+    <t>110000</t>
+  </si>
+  <si>
+    <t>111000</t>
+  </si>
+  <si>
+    <t>112000</t>
+  </si>
+  <si>
+    <t>113000</t>
+  </si>
+  <si>
+    <t>114000</t>
+  </si>
+  <si>
+    <t>115000</t>
+  </si>
+  <si>
+    <t>116000</t>
+  </si>
+  <si>
+    <t>117000</t>
+  </si>
+  <si>
+    <t>118000</t>
+  </si>
+  <si>
+    <t>119000</t>
+  </si>
+  <si>
+    <t>120000</t>
+  </si>
+  <si>
+    <t>121000</t>
+  </si>
+  <si>
+    <t>122000</t>
+  </si>
+  <si>
+    <t>123000</t>
+  </si>
+  <si>
+    <t>124000</t>
+  </si>
+  <si>
+    <t>125000</t>
+  </si>
+  <si>
+    <t>126000</t>
+  </si>
+  <si>
+    <t>127000</t>
+  </si>
+  <si>
+    <t>128000</t>
+  </si>
+  <si>
+    <t>129000</t>
+  </si>
+  <si>
+    <t>130000</t>
+  </si>
+  <si>
+    <t>131000</t>
+  </si>
+  <si>
+    <t>132000</t>
+  </si>
+  <si>
+    <t>133000</t>
+  </si>
+  <si>
+    <t>134000</t>
+  </si>
+  <si>
+    <t>135000</t>
+  </si>
+  <si>
+    <t>136000</t>
+  </si>
+  <si>
+    <t>137000</t>
+  </si>
+  <si>
+    <t>138000</t>
+  </si>
+  <si>
+    <t>139000</t>
+  </si>
+  <si>
+    <t>140000</t>
+  </si>
+  <si>
+    <t>141000</t>
+  </si>
+  <si>
+    <t>142000</t>
+  </si>
+  <si>
+    <t>143000</t>
+  </si>
+  <si>
+    <t>144000</t>
+  </si>
+  <si>
+    <t>145000</t>
+  </si>
+  <si>
+    <t>146000</t>
+  </si>
+  <si>
+    <t>147000</t>
+  </si>
+  <si>
+    <t>148000</t>
+  </si>
+  <si>
+    <t>149000</t>
+  </si>
+  <si>
+    <t>150000</t>
+  </si>
+  <si>
+    <t>151000</t>
+  </si>
+  <si>
+    <t>152000</t>
+  </si>
+  <si>
+    <t>153000</t>
+  </si>
+  <si>
+    <t>154000</t>
+  </si>
+  <si>
+    <t>155000</t>
+  </si>
+  <si>
+    <t>156000</t>
+  </si>
+  <si>
+    <t>157000</t>
+  </si>
+  <si>
+    <t>158000</t>
+  </si>
+  <si>
+    <t>159000</t>
+  </si>
+  <si>
+    <t>160000</t>
+  </si>
+  <si>
+    <t>161000</t>
+  </si>
+  <si>
+    <t>162000</t>
+  </si>
+  <si>
+    <t>163000</t>
+  </si>
+  <si>
+    <t>164000</t>
+  </si>
+  <si>
+    <t>165000</t>
+  </si>
+  <si>
+    <t>166000</t>
+  </si>
+  <si>
+    <t>167000</t>
+  </si>
+  <si>
+    <t>168000</t>
+  </si>
+  <si>
+    <t>169000</t>
+  </si>
+  <si>
+    <t>170000</t>
+  </si>
+  <si>
+    <t>171000</t>
+  </si>
+  <si>
+    <t>172000</t>
+  </si>
+  <si>
+    <t>173000</t>
+  </si>
+  <si>
+    <t>174000</t>
+  </si>
+  <si>
+    <t>175000</t>
+  </si>
+  <si>
+    <t>176000</t>
+  </si>
+  <si>
+    <t>177000</t>
+  </si>
+  <si>
+    <t>178000</t>
+  </si>
+  <si>
+    <t>179000</t>
+  </si>
+  <si>
+    <t>180000</t>
+  </si>
+  <si>
+    <t>181000</t>
+  </si>
+  <si>
+    <t>182000</t>
+  </si>
+  <si>
+    <t>183000</t>
+  </si>
+  <si>
+    <t>184000</t>
+  </si>
+  <si>
+    <t>185000</t>
+  </si>
+  <si>
+    <t>186000</t>
+  </si>
+  <si>
+    <t>187000</t>
+  </si>
+  <si>
+    <t>188000</t>
+  </si>
+  <si>
+    <t>189000</t>
+  </si>
+  <si>
+    <t>190000</t>
+  </si>
+  <si>
+    <t>191000</t>
+  </si>
+  <si>
+    <t>192000</t>
+  </si>
+  <si>
+    <t>193000</t>
+  </si>
+  <si>
+    <t>194000</t>
+  </si>
+  <si>
+    <t>195000</t>
+  </si>
+  <si>
+    <t>196000</t>
+  </si>
+  <si>
+    <t>197000</t>
+  </si>
+  <si>
+    <t>198000</t>
+  </si>
+  <si>
+    <t>199000</t>
+  </si>
+  <si>
+    <t>200000</t>
   </si>
 </sst>
 </file>
